--- a/InputData/elec/DATAiRC/Demand Altering Tech Assistance in RPS Compliance.xlsx
+++ b/InputData/elec/DATAiRC/Demand Altering Tech Assistance in RPS Compliance.xlsx
@@ -1,128 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\DATAiRC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\elec\DATAiRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C90061-3DBA-4E04-9ED2-918AFB1C450F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30F9454-BC3C-4F78-87C0-272E35954CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23715" yWindow="660" windowWidth="31410" windowHeight="20160" xr2:uid="{550EA44B-DE2C-417A-8238-32296907F5A3}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="DATAiRC" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Typically when setting an RPS value of 100%, there comes a point when the model needs to build a large</t>
+  </si>
+  <si>
+    <t>amount of capacity per year to meet the RPS (relative to prior years), often very near to 100%.</t>
+  </si>
+  <si>
+    <t>For instance, in the U.S. model in EPS 4.0.0, we see a significant increase in construction needed when</t>
+  </si>
+  <si>
+    <t>Typically, demand-altering technologies (such as batteries, demand response programs, etc.) assist</t>
+  </si>
+  <si>
+    <t>in reducing net peak load.  However, they could instead be operated to make it easier to comply with</t>
+  </si>
+  <si>
+    <t>going from 96% to 100% RPS.  This is due to the need to supply RPS-qualifying electricity even in the small</t>
+  </si>
+  <si>
+    <t>number of hours when it is most difficult to do so.</t>
+  </si>
+  <si>
+    <t>an RPS (i.e., by shifting demand away from the hours when it is most difficult to comply with the RPS).</t>
+  </si>
+  <si>
+    <t>In testing, this can have a limited but non-zero effect in reducing required capacity construction as an</t>
+  </si>
+  <si>
+    <t>RPS approaches 100%.</t>
+  </si>
+  <si>
+    <t>technologies so as to reduce net peak load or so as to facilitate RPS compliance.</t>
+  </si>
+  <si>
+    <t>Share of Demand-Altering Technologies Used to Facilitate RPS Compliance</t>
+  </si>
   <si>
     <t>DATAiRC Demand-Altering Technology Assistance in RPS Compliance</t>
   </si>
   <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
     <t>calibrated, see notes below</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Typically when setting an RPS value of 100%, there comes a point when the model needs to build a large</t>
-  </si>
-  <si>
-    <t>amount of capacity per year to meet the RPS (relative to prior years), often very near to 100%.</t>
-  </si>
-  <si>
-    <t>For instance, in the U.S. model in EPS 4.0.0, we see a significant increase in construction needed when</t>
-  </si>
-  <si>
-    <t>going from 96% to 100% RPS.  This is due to the need to supply RPS-qualifying electricity even in the small</t>
-  </si>
-  <si>
-    <t>number of hours when it is most difficult to do so.</t>
-  </si>
-  <si>
-    <t>Typically, demand-altering technologies (such as batteries, demand response programs, etc.) assist</t>
-  </si>
-  <si>
-    <t>in reducing net peak load.  However, they could instead be operated to make it easier to comply with</t>
-  </si>
-  <si>
-    <t>an RPS (i.e., by shifting demand away from the hours when it is most difficult to comply with the RPS).</t>
-  </si>
-  <si>
-    <t>In testing, this can have a limited but non-zero effect in reducing required capacity construction as an</t>
-  </si>
-  <si>
-    <t>RPS approaches 100%.</t>
-  </si>
-  <si>
     <t>This variable describes how utilities make decisions about whether to operate demand-altering</t>
   </si>
   <si>
-    <t>technologies so as to reduce net peak load or so as to facilitate RPS compliance.</t>
+    <t>Implementation Notes</t>
+  </si>
+  <si>
+    <t>This variable is designed to supply data to a GET DIRECT LOOKUPS() function in Vensim</t>
+  </si>
+  <si>
+    <t>because the indepdent variable is the RPS percentage, not time.  (If the independent variable</t>
+  </si>
+  <si>
+    <t>were time, a GET DIRECT DATA() function would be used.)</t>
+  </si>
+  <si>
+    <t>You may add as many ordered pairs of RPS percentage and demand-altering technology shares</t>
+  </si>
+  <si>
+    <t>However, there must always be an entry for a zero RPS share and an entry for a 1 (i.e. 100%) RPS share.</t>
+  </si>
+  <si>
+    <t>Vensim linearly interpolates between the data points provided, so if you do not want linear interpolation,</t>
+  </si>
+  <si>
+    <t>add more data points to more precisely define the shape of the curve you desire.  A graph is included</t>
+  </si>
+  <si>
+    <t>in the blue output tab to help visualize the curve you are creating.</t>
+  </si>
+  <si>
+    <t>RPS Share</t>
+  </si>
+  <si>
+    <t>as you wish to the blue output tab.</t>
   </si>
   <si>
     <t>Curves may be specified separately for diurnal and for seasonal technologies</t>
   </si>
   <si>
-    <t>Implementation Notes</t>
-  </si>
-  <si>
-    <t>This variable is designed to supply data to a GET DIRECT LOOKUPS() function in Vensim</t>
-  </si>
-  <si>
-    <t>because the indepdent variable is the RPS percentage, not time.  (If the independent variable</t>
-  </si>
-  <si>
-    <t>were time, a GET DIRECT DATA() function would be used.)</t>
-  </si>
-  <si>
-    <t>You may add as many ordered pairs of RPS percentage and demand-altering technology shares</t>
-  </si>
-  <si>
-    <t>as you wish to the blue output tab.</t>
-  </si>
-  <si>
-    <t>However, there must always be an entry for a zero RPS share and an entry for a 1 (i.e. 100%) RPS share.</t>
-  </si>
-  <si>
-    <t>Vensim linearly interpolates between the data points provided, so if you do not want linear interpolation,</t>
-  </si>
-  <si>
-    <t>add more data points to more precisely define the shape of the curve you desire.  A graph is included</t>
-  </si>
-  <si>
-    <t>in the blue output tab to help visualize the curve you are creating.</t>
+    <t>Duirnal Demand-Altering Technologies</t>
+  </si>
+  <si>
+    <t>Seasonal Demand-Altering Technologies</t>
   </si>
   <si>
     <t>Do not alter the rows (i.e., by adding or removing rows), as Vensim expects the data to be on these specific</t>
   </si>
   <si>
     <t>rows (and to start in the second column).</t>
-  </si>
-  <si>
-    <t>Duirnal Demand-Altering Technologies</t>
-  </si>
-  <si>
-    <t>RPS Share</t>
-  </si>
-  <si>
-    <t>Share of Demand-Altering Technologies Used to Facilitate RPS Compliance</t>
-  </si>
-  <si>
-    <t>Seasonal Demand-Altering Technologies</t>
   </si>
 </sst>
 </file>
@@ -223,7 +236,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -244,9 +257,26 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -273,9 +303,9 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -288,8 +318,8 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:prstDash val="solid"/>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -331,7 +361,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C94E-4915-902D-5EB3FA338994}"/>
+              <c16:uniqueId val="{00000000-B7E8-4F4C-A872-0D79DF5A02B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -364,9 +394,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -376,7 +406,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -397,9 +427,26 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
-              <a:prstDash val="solid"/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -414,16 +461,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -457,9 +504,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -469,7 +516,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -490,9 +537,26 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
-              <a:prstDash val="solid"/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -507,16 +571,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -532,9 +596,23 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -548,10 +626,24 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -581,7 +673,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -602,9 +694,26 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -631,9 +740,9 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
@@ -646,8 +755,8 @@
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:prstDash val="solid"/>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -689,7 +798,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-859D-4E94-8AC9-92483BF52C0C}"/>
+              <c16:uniqueId val="{00000000-1081-40A8-BAF4-96F0D96502AB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -722,9 +831,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -734,7 +843,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -755,9 +864,26 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
-              <a:prstDash val="solid"/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -772,16 +898,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -815,9 +941,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:title>
@@ -827,7 +953,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -848,9 +974,26 @@
             <a:noFill/>
             <a:ln>
               <a:noFill/>
-              <a:prstDash val="solid"/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -865,16 +1008,16 @@
                 <a:lumOff val="75000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
@@ -890,9 +1033,23 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -906,16 +1063,1142 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -938,7 +2221,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C874A59-0843-BF31-FF5A-1514ECDA5C93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -974,11 +2257,13 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECDE0120-8F83-4B50-ADEB-F74D76067CF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1291,7 +2576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C829B1ED-06E0-4E5A-85BE-4FC9634EDEAC}">
   <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1300,149 +2585,146 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="3"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1451,7 +2733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D9A127-BDBB-4A3E-9045-3B8D75D8CD6A}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
@@ -1463,12 +2745,12 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1482,7 +2764,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1496,12 +2778,12 @@
     </row>
     <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1515,7 +2797,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>0</v>
